--- a/sablona.xlsx
+++ b/sablona.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\OneDrive\Dokumenty\Work\Cettus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\source\repos\_webs\Job-Recorder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FDE091-8D34-45AE-AE52-501E811340C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6FF123-6E0A-4961-AE1E-FEEFEFCB539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4752" yWindow="2616" windowWidth="23040" windowHeight="13560" xr2:uid="{C6B4764B-D8E4-4161-8894-EBCE4ACDC8CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{C6B4764B-D8E4-4161-8894-EBCE4ACDC8CD}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -592,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E191A2-8BE1-4102-8AA8-A64B3D030B27}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="13" bestFit="1" customWidth="1"/>
@@ -735,69 +735,69 @@
       <c r="J8" s="12"/>
       <c r="K8" s="24"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="25"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="10" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="25"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="26">
-        <f>SUM(K3:K9)</f>
+      <c r="K15" s="26">
+        <f>SUM(K3:K14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="10" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K16" s="24">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="10" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="20">
-        <f>K10*K11</f>
+      <c r="K17" s="20">
+        <f>K15*K16</f>
         <v>0</v>
       </c>
     </row>

--- a/sablona.xlsx
+++ b/sablona.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\source\repos\_webs\Job-Recorder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6FF123-6E0A-4961-AE1E-FEEFEFCB539E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F797AC-2DF4-4492-B007-9FC0BC6EB8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{C6B4764B-D8E4-4161-8894-EBCE4ACDC8CD}"/>
   </bookViews>
@@ -592,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E191A2-8BE1-4102-8AA8-A64B3D030B27}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="13" bestFit="1" customWidth="1"/>
@@ -707,7 +707,7 @@
       <c r="H6" s="6"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="24"/>
+      <c r="K6" s="28"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="22"/>
@@ -720,7 +720,7 @@
       <c r="H7" s="6"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
-      <c r="K7" s="24"/>
+      <c r="K7" s="28"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="22"/>
@@ -733,71 +733,119 @@
       <c r="H8" s="6"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="24"/>
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="22"/>
+      <c r="E9" s="6"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="28"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="E10" s="6"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="28"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="22"/>
+      <c r="E11" s="6"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="28"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="22"/>
+      <c r="E12" s="6"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="28"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="22"/>
+      <c r="E13" s="6"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="28"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="23"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="25"/>
+      <c r="A14" s="22"/>
+      <c r="E14" s="6"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="10" t="s">
+      <c r="A15" s="22"/>
+      <c r="E15" s="6"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="28"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="22"/>
+      <c r="E16" s="6"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="28"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="23"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="26">
-        <f>SUM(K3:K14)</f>
+      <c r="K18" s="26">
+        <f>SUM(K3:K17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="10" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K19" s="24">
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="10" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="20">
-        <f>K15*K16</f>
+      <c r="K20" s="20">
+        <f>K18*K19</f>
         <v>0</v>
       </c>
     </row>
